--- a/data/trans_orig/P16A12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4907</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5265</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489830</t>
+          <t>489195</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>467489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956288</t>
+          <t>956646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>10411</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>728321</t>
+          <t>725078</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619089</t>
+          <t>619025</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348581</t>
+          <t>1349057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360090</t>
+          <t>1360093</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>25967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618537</t>
+          <t>618488</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631885</t>
+          <t>631799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676412</t>
+          <t>676701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687532</t>
+          <t>687547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300565</t>
+          <t>1301427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1317005</t>
+          <t>1316744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35758</t>
+          <t>36587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>26505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27947</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>54744</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>483389</t>
+          <t>482560</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504275</t>
+          <t>503483</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488724</t>
+          <t>489137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>505532</t>
+          <t>504795</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>981028</t>
+          <t>980045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1006842</t>
+          <t>1006428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60956</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30172</t>
+          <t>29405</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53699</t>
+          <t>55047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>72218</t>
+          <t>71620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109746</t>
+          <t>106325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>325754</t>
+          <t>324148</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>350836</t>
+          <t>351191</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>350287</t>
+          <t>348939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>373814</t>
+          <t>374581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>680950</t>
+          <t>684371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718478</t>
+          <t>719076</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44698</t>
+          <t>45316</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70865</t>
+          <t>71941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56230</t>
+          <t>57761</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86371</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111097</t>
+          <t>110393</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147966</t>
+          <t>149360</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221718</t>
+          <t>220642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247885</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>256563</t>
+          <t>257533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286704</t>
+          <t>285173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487551</t>
+          <t>486157</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>524420</t>
+          <t>525124</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31167</t>
+          <t>31574</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>53989</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53614</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92057</t>
+          <t>93298</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>130980</t>
+          <t>131671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156130</t>
+          <t>155894</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178716</t>
+          <t>178309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>250037</t>
+          <t>251248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>280294</t>
+          <t>280108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>412811</t>
+          <t>412120</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>451734</t>
+          <t>450493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>159289</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209442</t>
+          <t>209717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177613</t>
+          <t>178922</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237097</t>
+          <t>234057</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>349023</t>
+          <t>352733</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>424353</t>
+          <t>426803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3066083</t>
+          <t>3065808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3116555</t>
+          <t>3116236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3142100</t>
+          <t>3145140</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3201584</t>
+          <t>3200275</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6230369</t>
+          <t>6227919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6305699</t>
+          <t>6301989</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9083</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>11444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446631</t>
+          <t>446529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>420256</t>
+          <t>421300</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428354</t>
+          <t>428347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871581</t>
+          <t>871001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880546</t>
+          <t>880533</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14532</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>666044</t>
+          <t>666545</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681395</t>
+          <t>681400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>594682</t>
+          <t>593714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606287</t>
+          <t>606222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1265607</t>
+          <t>1265130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1284055</t>
+          <t>1284629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671065</t>
+          <t>670448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679134</t>
+          <t>679122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>685780</t>
+          <t>685638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699815</t>
+          <t>699667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1360746</t>
+          <t>1360615</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1376781</t>
+          <t>1376208</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32637</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59148</t>
+          <t>58762</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581112</t>
+          <t>581537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600927</t>
+          <t>600263</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>582495</t>
+          <t>581391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601072</t>
+          <t>601111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1169541</t>
+          <t>1169927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1196052</t>
+          <t>1197577</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36871</t>
+          <t>37112</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64160</t>
+          <t>64561</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39355</t>
+          <t>40143</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>66286</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83265</t>
+          <t>83809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120766</t>
+          <t>124648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364184</t>
+          <t>363783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>391473</t>
+          <t>391232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>380003</t>
+          <t>381514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>408445</t>
+          <t>407657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>755378</t>
+          <t>751496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>792879</t>
+          <t>792335</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73502</t>
+          <t>74678</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107919</t>
+          <t>108809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68871</t>
+          <t>69180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100589</t>
+          <t>101498</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152310</t>
+          <t>152875</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>200546</t>
+          <t>199696</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201867</t>
+          <t>200977</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236284</t>
+          <t>235108</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253407</t>
+          <t>252498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285125</t>
+          <t>284816</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463236</t>
+          <t>464086</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511472</t>
+          <t>510907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57735</t>
+          <t>56455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87966</t>
+          <t>87079</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98880</t>
+          <t>100497</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>135017</t>
+          <t>137185</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167835</t>
+          <t>167809</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>215459</t>
+          <t>216222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,01%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161070</t>
+          <t>161957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>191301</t>
+          <t>192581</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>251736</t>
+          <t>249568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>287873</t>
+          <t>286256</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>420330</t>
+          <t>419567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467954</t>
+          <t>467980</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219446</t>
+          <t>221138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>282832</t>
+          <t>284347</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>269319</t>
+          <t>266721</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>335355</t>
+          <t>333511</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>502682</t>
+          <t>502880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>599412</t>
+          <t>592595</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3138347</t>
+          <t>3136832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3201733</t>
+          <t>3200041</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3211755</t>
+          <t>3213599</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3277791</t>
+          <t>3280389</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6368877</t>
+          <t>6375694</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6465607</t>
+          <t>6465409</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,62 +6726,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4281</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414696</t>
+          <t>413803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810937</t>
+          <t>810541</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10769</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583468</t>
+          <t>583520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556273</t>
+          <t>556034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562665</t>
+          <t>562663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143271</t>
+          <t>1143493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152220</t>
+          <t>1152191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>15709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24854</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>652813</t>
+          <t>653388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665034</t>
+          <t>665081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647288</t>
+          <t>647264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657770</t>
+          <t>657760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305629</t>
+          <t>1305271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320963</t>
+          <t>1320780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25514</t>
+          <t>24299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49376</t>
+          <t>49604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>13287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>31588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42690</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74870</t>
+          <t>73404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596672</t>
+          <t>596444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>620534</t>
+          <t>621749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>617840</t>
+          <t>617489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>636179</t>
+          <t>635790</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1220255</t>
+          <t>1221721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1252435</t>
+          <t>1253141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>47149</t>
+          <t>46058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75962</t>
+          <t>77821</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72636</t>
+          <t>74135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98262</t>
+          <t>97872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141620</t>
+          <t>138445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>401956</t>
+          <t>400097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430769</t>
+          <t>431860</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424213</t>
+          <t>422714</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454075</t>
+          <t>452895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>833147</t>
+          <t>836322</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876505</t>
+          <t>876895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>75200</t>
+          <t>74372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108754</t>
+          <t>107890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68996</t>
+          <t>69440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101629</t>
+          <t>103076</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>154198</t>
+          <t>152450</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>197681</t>
+          <t>198801</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225576</t>
+          <t>226440</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259130</t>
+          <t>259958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276133</t>
+          <t>274686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308766</t>
+          <t>308322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>514411</t>
+          <t>513291</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>557894</t>
+          <t>559642</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,59%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72571</t>
+          <t>72663</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98984</t>
+          <t>100211</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84993</t>
+          <t>86437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125861</t>
+          <t>127941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>169171</t>
+          <t>170010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216410</t>
+          <t>217809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>158014</t>
+          <t>156787</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184427</t>
+          <t>184335</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>274308</t>
+          <t>272228</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>315176</t>
+          <t>313732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>440757</t>
+          <t>439358</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>487996</t>
+          <t>487157</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>253157</t>
+          <t>252972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>316850</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,82 +9107,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>277943</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>247421</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>316075</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>561750</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>517427</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>610129</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>277943</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>246106</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>313433</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>561750</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>517317</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>608821</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3077500</t>
+          <t>3078074</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3141193</t>
+          <t>3141378</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3231109</t>
+          <t>3228467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3298436</t>
+          <t>3297121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6330071</t>
+          <t>6328763</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6421575</t>
+          <t>6421465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicinas para la diabetes en las dos últimas semanas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5468</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1086</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5907</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6202</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307293</t>
+          <t>307732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706985</t>
+          <t>707364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412665</t>
+          <t>415643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507338</t>
+          <t>507564</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>924248</t>
+          <t>923011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17625</t>
+          <t>17686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518713</t>
+          <t>518652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531000</t>
+          <t>531200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532273</t>
+          <t>532796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540059</t>
+          <t>540090</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1055728</t>
+          <t>1054917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069756</t>
+          <t>1069195</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64226</t>
+          <t>65338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28391</t>
+          <t>27793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79317</t>
+          <t>81605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>823560</t>
+          <t>822448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>869135</t>
+          <t>870647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>684490</t>
+          <t>685088</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698801</t>
+          <t>698915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1521350</t>
+          <t>1519062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1565523</t>
+          <t>1563240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57760</t>
+          <t>57014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86626</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>45056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91742</t>
+          <t>92514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127490</t>
+          <t>124923</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>473611</t>
+          <t>472828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502477</t>
+          <t>503223</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>499557</t>
+          <t>499831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516832</t>
+          <t>516134</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977634</t>
+          <t>980201</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013382</t>
+          <t>1012610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65070</t>
+          <t>65096</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88649</t>
+          <t>90877</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101951</t>
+          <t>102099</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78219</t>
+          <t>77131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186466</t>
+          <t>187610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279516</t>
+          <t>277288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303095</t>
+          <t>303069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>506417</t>
+          <t>506269</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580448</t>
+          <t>580589</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>790067</t>
+          <t>788923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>898314</t>
+          <t>899402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>68381</t>
+          <t>67778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>91802</t>
+          <t>92137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>113251</t>
+          <t>112567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>138026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188488</t>
+          <t>188118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>224599</t>
+          <t>222992</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190957</t>
+          <t>190622</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214378</t>
+          <t>214981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285914</t>
+          <t>286699</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311474</t>
+          <t>312158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>482885</t>
+          <t>484492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>518996</t>
+          <t>519366</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,41%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>222751</t>
+          <t>211549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>319679</t>
+          <t>319523</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>203062</t>
+          <t>207611</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280081</t>
+          <t>281874</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>470477</t>
+          <t>461231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>588927</t>
+          <t>586496</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3139141</t>
+          <t>3139297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3236069</t>
+          <t>3247271</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3377952</t>
+          <t>3376159</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3454971</t>
+          <t>3450422</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6527926</t>
+          <t>6530357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6646376</t>
+          <t>6655622</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A12-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P16A12-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489195</t>
+          <t>488707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>956646</t>
+          <t>955683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11925</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>725078</t>
+          <t>726572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>619025</t>
+          <t>617293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1349057</t>
+          <t>1348711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1360093</t>
+          <t>1360099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>6393</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19161</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>10585</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>26986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618488</t>
+          <t>618699</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631799</t>
+          <t>631256</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676701</t>
+          <t>677294</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687547</t>
+          <t>687553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1301427</t>
+          <t>1300408</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316744</t>
+          <t>1316809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36587</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>26813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>29037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>53937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>482560</t>
+          <t>484182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>503483</t>
+          <t>504409</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>489137</t>
+          <t>488829</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>504795</t>
+          <t>505440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>980045</t>
+          <t>980852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1006428</t>
+          <t>1005752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62562</t>
+          <t>60467</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55047</t>
+          <t>53672</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70657</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106325</t>
+          <t>105579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>324148</t>
+          <t>326243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>351191</t>
+          <t>350827</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>348939</t>
+          <t>350314</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>374581</t>
+          <t>373521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684371</t>
+          <t>685117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719076</t>
+          <t>720039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,06%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45316</t>
+          <t>45734</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71941</t>
+          <t>70623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57761</t>
+          <t>57688</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85401</t>
+          <t>86776</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110393</t>
+          <t>109464</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>149360</t>
+          <t>148197</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220642</t>
+          <t>221960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>247267</t>
+          <t>246849</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>257533</t>
+          <t>256158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285173</t>
+          <t>285246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>486157</t>
+          <t>487320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525124</t>
+          <t>526053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31574</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53989</t>
+          <t>53671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>53418</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82660</t>
+          <t>84769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93298</t>
+          <t>91992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131671</t>
+          <t>130154</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>155894</t>
+          <t>156212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178309</t>
+          <t>178522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>251248</t>
+          <t>249139</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>280108</t>
+          <t>280490</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>412120</t>
+          <t>413637</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>450493</t>
+          <t>451799</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159289</t>
+          <t>158228</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>209717</t>
+          <t>209691</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>177006</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234057</t>
+          <t>231537</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>352733</t>
+          <t>352579</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>426803</t>
+          <t>428694</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3065808</t>
+          <t>3065834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3116236</t>
+          <t>3117297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3145140</t>
+          <t>3147660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3200275</t>
+          <t>3202191</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6227919</t>
+          <t>6226028</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6301989</t>
+          <t>6302143</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11444</t>
+          <t>10949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446529</t>
+          <t>446567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421300</t>
+          <t>421229</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428347</t>
+          <t>428349</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>871001</t>
+          <t>871496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880533</t>
+          <t>880552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4838</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19723</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10122</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30321</t>
+          <t>28118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>666545</t>
+          <t>666515</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>681400</t>
+          <t>681404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>593714</t>
+          <t>593627</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>606222</t>
+          <t>606183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1265130</t>
+          <t>1267333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1284629</t>
+          <t>1285329</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20297</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>24982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670448</t>
+          <t>670098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679122</t>
+          <t>679020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>685638</t>
+          <t>685572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>699667</t>
+          <t>699070</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1360615</t>
+          <t>1361007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1376208</t>
+          <t>1376766</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>33578</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>13449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58762</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>581537</t>
+          <t>581039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>600263</t>
+          <t>600158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>581391</t>
+          <t>581129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>601111</t>
+          <t>600623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1169927</t>
+          <t>1168888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1197577</t>
+          <t>1196522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37112</t>
+          <t>37495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64561</t>
+          <t>64791</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40143</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66286</t>
+          <t>67612</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83809</t>
+          <t>83061</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124648</t>
+          <t>120834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>363783</t>
+          <t>363553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>391232</t>
+          <t>390849</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>381514</t>
+          <t>380188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>407657</t>
+          <t>408508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751496</t>
+          <t>755310</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>792335</t>
+          <t>793083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74678</t>
+          <t>72600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>108809</t>
+          <t>108965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>69363</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101498</t>
+          <t>101062</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152875</t>
+          <t>152386</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199696</t>
+          <t>199028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200977</t>
+          <t>200821</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>235108</t>
+          <t>237186</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>252498</t>
+          <t>252934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>284816</t>
+          <t>284633</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464086</t>
+          <t>464754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>510907</t>
+          <t>511396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,04%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56455</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87079</t>
+          <t>87209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>100497</t>
+          <t>99329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137185</t>
+          <t>138344</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>167809</t>
+          <t>167190</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216222</t>
+          <t>216002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161957</t>
+          <t>161827</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192581</t>
+          <t>191388</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>249568</t>
+          <t>248409</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286256</t>
+          <t>287424</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419567</t>
+          <t>419787</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>467980</t>
+          <t>468599</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221138</t>
+          <t>218039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>284347</t>
+          <t>282352</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>266721</t>
+          <t>267237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>333511</t>
+          <t>332385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>502880</t>
+          <t>506456</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>592595</t>
+          <t>597037</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3136832</t>
+          <t>3138827</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3200041</t>
+          <t>3203140</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3213599</t>
+          <t>3214725</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3280389</t>
+          <t>3279873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6375694</t>
+          <t>6371252</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6465409</t>
+          <t>6461833</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413803</t>
+          <t>414763</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810541</t>
+          <t>810544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10547</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583520</t>
+          <t>583430</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>556034</t>
+          <t>556077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562663</t>
+          <t>562664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143493</t>
+          <t>1142844</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1152191</t>
+          <t>1152170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15709</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13440</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9703</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>653388</t>
+          <t>651519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665081</t>
+          <t>665180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>647264</t>
+          <t>647946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657760</t>
+          <t>658519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305271</t>
+          <t>1306074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1320780</t>
+          <t>1320865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49604</t>
+          <t>49687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31588</t>
+          <t>31217</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73404</t>
+          <t>74290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>596444</t>
+          <t>596361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>621749</t>
+          <t>621348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>617489</t>
+          <t>617860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635790</t>
+          <t>636291</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1221721</t>
+          <t>1220835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1253141</t>
+          <t>1252384</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46058</t>
+          <t>46912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>77821</t>
+          <t>77502</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43954</t>
+          <t>44581</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74135</t>
+          <t>73630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97872</t>
+          <t>97461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138445</t>
+          <t>141090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400097</t>
+          <t>400416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431860</t>
+          <t>431006</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>422714</t>
+          <t>423219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>452895</t>
+          <t>452268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>836322</t>
+          <t>833677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876895</t>
+          <t>877306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74372</t>
+          <t>74341</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>107890</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69440</t>
+          <t>67041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103076</t>
+          <t>100759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>152450</t>
+          <t>151634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>198801</t>
+          <t>199411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226440</t>
+          <t>227294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259958</t>
+          <t>259989</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274686</t>
+          <t>277003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308322</t>
+          <t>310721</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>513291</t>
+          <t>512681</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>559642</t>
+          <t>560458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72663</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100211</t>
+          <t>100270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86437</t>
+          <t>86591</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>127941</t>
+          <t>128166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>170010</t>
+          <t>167149</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>217809</t>
+          <t>216765</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156787</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>184335</t>
+          <t>184840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>272228</t>
+          <t>272003</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>313732</t>
+          <t>313578</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439358</t>
+          <t>440402</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>487157</t>
+          <t>490018</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>252972</t>
+          <t>252521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>316276</t>
+          <t>313703</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>247421</t>
+          <t>245451</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>316075</t>
+          <t>315598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>517427</t>
+          <t>517451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>610129</t>
+          <t>605904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3078074</t>
+          <t>3080647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3141378</t>
+          <t>3141829</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3228467</t>
+          <t>3228944</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3297121</t>
+          <t>3299091</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6328763</t>
+          <t>6332988</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6421465</t>
+          <t>6421441</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5468</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9813,22 +9813,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312114</t>
+          <t>361407</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307732</t>
+          <t>356180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -9848,27 +9848,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>712101</t>
+          <t>769200</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>707364</t>
+          <t>764225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>776</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12040</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421611</t>
+          <t>475002</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415643</t>
+          <t>467202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,27 +10156,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510701</t>
+          <t>500307</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>507564</t>
+          <t>496428</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10191,27 +10191,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932312</t>
+          <t>975309</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>923011</t>
+          <t>966893</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>6321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>3561</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>28745</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>526071</t>
+          <t>608530</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518652</t>
+          <t>600502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531200</t>
+          <t>614516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>537287</t>
+          <t>615013</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>532796</t>
+          <t>609594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540090</t>
+          <t>618578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1063358</t>
+          <t>1223543</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1054917</t>
+          <t>1214231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069195</t>
+          <t>1230853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>41226</t>
+          <t>45143</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>34009</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65338</t>
+          <t>60929</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20030</t>
+          <t>21461</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27793</t>
+          <t>30025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>51489</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81605</t>
+          <t>82603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>846560</t>
+          <t>655474</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822448</t>
+          <t>639688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870647</t>
+          <t>666608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>692851</t>
+          <t>715425</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>685088</t>
+          <t>706861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698915</t>
+          <t>721424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1539412</t>
+          <t>1370899</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1519062</t>
+          <t>1354901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1563240</t>
+          <t>1386015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71811</t>
+          <t>77926</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57014</t>
+          <t>62854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87409</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36169</t>
+          <t>40734</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45056</t>
+          <t>50646</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>107980</t>
+          <t>118660</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>92514</t>
+          <t>100220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124923</t>
+          <t>136471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>488426</t>
+          <t>530433</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>472828</t>
+          <t>515209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>503223</t>
+          <t>545505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>508718</t>
+          <t>566714</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>499831</t>
+          <t>556802</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>516134</t>
+          <t>575810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>997144</t>
+          <t>1097147</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>980201</t>
+          <t>1079336</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1012610</t>
+          <t>1115587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544887</t>
+          <t>607448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105124</t>
+          <t>1215807</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77108</t>
+          <t>81937</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65096</t>
+          <t>67875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90877</t>
+          <t>96821</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>64503</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102099</t>
+          <t>81474</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>141611</t>
+          <t>152123</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>135108</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187610</t>
+          <t>169043</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>291057</t>
+          <t>325143</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>277288</t>
+          <t>310259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>303069</t>
+          <t>339205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>543865</t>
+          <t>368980</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>506269</t>
+          <t>357692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580589</t>
+          <t>379220</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>834922</t>
+          <t>694123</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>788923</t>
+          <t>677203</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>899402</t>
+          <t>711138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>79761</t>
+          <t>86954</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67778</t>
+          <t>74101</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92137</t>
+          <t>100196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>125946</t>
+          <t>135858</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112567</t>
+          <t>123194</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>138026</t>
+          <t>151135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>205706</t>
+          <t>222813</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>188118</t>
+          <t>203362</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222992</t>
+          <t>240605</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,1%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>202998</t>
+          <t>223244</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>190622</t>
+          <t>210002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214981</t>
+          <t>236097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>298779</t>
+          <t>327552</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>286699</t>
+          <t>312275</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>312158</t>
+          <t>340216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>501778</t>
+          <t>550795</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>484492</t>
+          <t>533003</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>519366</t>
+          <t>570246</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>424725</t>
+          <t>463410</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707484</t>
+          <t>773608</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,69 +12066,69 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>282108</t>
+          <t>306157</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>211549</t>
+          <t>277521</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>319523</t>
+          <t>339357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,61%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>277246</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>254897</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>304505</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>7,43%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>8,16%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>9,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>253717</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>207611</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>281874</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>927</t>
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>535825</t>
+          <t>583403</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>461231</t>
+          <t>545388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>586496</t>
+          <t>624473</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -12179,67 +12179,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3176712</t>
+          <t>3225618</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3139297</t>
+          <t>3192418</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3247271</t>
+          <t>3254254</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>90,39%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>4838</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3455399</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3428140</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3477748</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>92,57%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>91,84%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>90,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4838</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3404316</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3376159</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3450422</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>93,06%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6581028</t>
+          <t>6681016</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6530357</t>
+          <t>6639946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6655622</t>
+          <t>6719031</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3458820</t>
+          <t>3531775</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3658033</t>
+          <t>3732645</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7116853</t>
+          <t>7264419</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
